--- a/Jihozlar_Smetasi.xlsx
+++ b/Jihozlar_Smetasi.xlsx
@@ -1,12 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E4B047-9E5B-4D67-9799-F3F1B77B5A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Смета с изображениями" state="visible" r:id="rId4"/>
+    <sheet name="Смета с изображениями" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -82,19 +99,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -120,7 +137,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -129,35 +146,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="double">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -170,26 +169,26 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -206,17 +205,17 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1000125"/>
+    <xdr:ext cx="5267325" cy="3950494"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -235,8 +234,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="0" y="381000"/>
+          <a:ext cx="5267325" cy="3950494"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -245,20 +244,20 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1000125"/>
+    <xdr:ext cx="5410200" cy="4057650"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -274,8 +273,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="0" y="4400550"/>
+          <a:ext cx="5410200" cy="4057650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -284,20 +283,20 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1000125"/>
+    <xdr:ext cx="5410200" cy="4057650"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -313,8 +312,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="0" y="9601200"/>
+          <a:ext cx="5410200" cy="4057650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -323,20 +322,20 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1000125"/>
+    <xdr:ext cx="5321300" cy="3990975"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4">
+        <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -352,8 +351,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="0" y="13677900"/>
+          <a:ext cx="5321300" cy="3990975"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -362,20 +361,20 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1000125"/>
+    <xdr:ext cx="4089400" cy="3067050"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5">
+        <xdr:cNvPr id="6" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -391,8 +390,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="0" y="18211800"/>
+          <a:ext cx="4089400" cy="3067050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -401,20 +400,20 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1000125"/>
+    <xdr:ext cx="5080000" cy="3810000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6">
+        <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -430,8 +429,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="0" y="21383625"/>
+          <a:ext cx="5080000" cy="3810000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -440,20 +439,20 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1000125"/>
+    <xdr:ext cx="5041900" cy="3781425"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7">
+        <xdr:cNvPr id="8" name="Picture 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -469,8 +468,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="0" y="25365075"/>
+          <a:ext cx="5041900" cy="3781425"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -479,20 +478,20 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1000125"/>
+    <xdr:ext cx="4940300" cy="3705225"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8">
+        <xdr:cNvPr id="9" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -508,8 +507,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="0" y="29317950"/>
+          <a:ext cx="4940300" cy="3705225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -518,20 +517,20 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1333500" cy="1000125"/>
+    <xdr:ext cx="4924425" cy="3693319"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 9">
+        <xdr:cNvPr id="10" name="Picture 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -540,15 +539,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="0" y="33642300"/>
+          <a:ext cx="4924425" cy="3693319"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -881,11 +880,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="82.42578125" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
@@ -894,7 +896,7 @@
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -917,7 +919,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="100" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="316.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>7</v>
@@ -935,10 +937,11 @@
         <v>2200892.85</v>
       </c>
       <c r="G2" s="5">
-        <f>D2*F2</f>
+        <f t="shared" ref="G2:G10" si="0">D2*F2</f>
+        <v>8803571.4000000004</v>
       </c>
     </row>
-    <row r="3" ht="100" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
         <v>10</v>
@@ -956,10 +959,11 @@
         <v>1096785.71</v>
       </c>
       <c r="G3" s="5">
-        <f>D3*F3</f>
+        <f t="shared" si="0"/>
+        <v>4387142.84</v>
       </c>
     </row>
-    <row r="4" ht="100" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="321" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
@@ -977,10 +981,11 @@
         <v>54857.14</v>
       </c>
       <c r="G4" s="5">
-        <f>D4*F4</f>
+        <f t="shared" si="0"/>
+        <v>219428.56</v>
       </c>
     </row>
-    <row r="5" ht="100" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="357" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="3" t="s">
         <v>14</v>
@@ -995,13 +1000,14 @@
         <v>9</v>
       </c>
       <c r="F5" s="5">
-        <v>1165816.6</v>
+        <v>1165816.6000000001</v>
       </c>
       <c r="G5" s="5">
-        <f>D5*F5</f>
+        <f t="shared" si="0"/>
+        <v>2331633.2000000002</v>
       </c>
     </row>
-    <row r="6" ht="100" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="249.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="3" t="s">
         <v>15</v>
@@ -1016,13 +1022,14 @@
         <v>9</v>
       </c>
       <c r="F6" s="5">
-        <v>51958.4</v>
+        <v>51958.400000000001</v>
       </c>
       <c r="G6" s="5">
-        <f>D6*F6</f>
+        <f t="shared" si="0"/>
+        <v>623500.80000000005</v>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="313.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="3" t="s">
         <v>16</v>
@@ -1040,10 +1047,11 @@
         <v>97422</v>
       </c>
       <c r="G7" s="5">
-        <f>D7*F7</f>
+        <f t="shared" si="0"/>
+        <v>389688</v>
       </c>
     </row>
-    <row r="8" ht="100" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="311.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="3" t="s">
         <v>17</v>
@@ -1061,10 +1069,11 @@
         <v>135711</v>
       </c>
       <c r="G8" s="5">
-        <f>D8*F8</f>
+        <f t="shared" si="0"/>
+        <v>1085688</v>
       </c>
     </row>
-    <row r="9" ht="100" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="340.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="3" t="s">
         <v>18</v>
@@ -1082,10 +1091,11 @@
         <v>2465000</v>
       </c>
       <c r="G9" s="5">
-        <f>D9*F9</f>
+        <f t="shared" si="0"/>
+        <v>9860000</v>
       </c>
     </row>
-    <row r="10" ht="100" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="301.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3" t="s">
         <v>19</v>
@@ -1103,10 +1113,11 @@
         <v>3631250</v>
       </c>
       <c r="G10" s="5">
-        <f>D10*F10</f>
+        <f t="shared" si="0"/>
+        <v>14525000</v>
       </c>
     </row>
-    <row r="11" ht="25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="7" t="s">
         <v>21</v>
@@ -1117,11 +1128,12 @@
       <c r="F11" s="6"/>
       <c r="G11" s="8">
         <f>SUM(G2:G10)</f>
+        <v>42225652.799999997</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <drawing r:id="rId1"/>
+  <pageSetup scale="41" fitToHeight="0" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>